--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -2060,7 +2060,7 @@
         <v>-0.1083872078851147</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
         <v>39132</v>
@@ -3518,10 +3518,10 @@
         <v>0.01198716095958136</v>
       </c>
       <c r="J56" t="n">
-        <v>12429</v>
+        <v>12269</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -8453,7 +8453,7 @@
         <v>-0.2240320427236315</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
         <v>-0.273000085741233</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -13422,10 +13422,10 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
@@ -18098,7 +18098,7 @@
         <v>-0.0183452577508714</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -21646,7 +21646,7 @@
         <v>-0.2094684083413405</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -25207,7 +25207,7 @@
         <v>-0.08594133115040216</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
         <v>34107</v>
@@ -26665,10 +26665,10 @@
         <v>0.006766597613598328</v>
       </c>
       <c r="J56" t="n">
-        <v>21045</v>
+        <v>21006</v>
       </c>
       <c r="K56" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
@@ -28755,7 +28755,7 @@
         <v>-0.06077669035170041</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
         <v>8182</v>
@@ -32266,7 +32266,7 @@
         <v>-0.1048811277088155</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -33724,10 +33724,10 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -35777,7 +35777,7 @@
         <v>-0.06141257536606374</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -37235,10 +37235,10 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -39288,7 +39288,7 @@
         <v>-0.07884485958436155</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -42836,7 +42836,7 @@
         <v>-0.08991228070175439</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -49229,7 +49229,7 @@
         <v>-0.062118512558193</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -50675,7 +50675,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>43070</v>
+        <v>43042</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -50684,7 +50684,7 @@
         <v>396</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.006087540217114552</v>
+        <v>0.005439437076128972</v>
       </c>
       <c r="J56" t="n">
         <v>7486</v>
@@ -50721,7 +50721,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.8594533658491694</v>
+        <v>-0.8593627699249505</v>
       </c>
       <c r="J57" t="n">
         <v>5118</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -26641,13 +26641,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>259251</v>
+        <v>259333</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.008103683598595465</v>
+        <v>0.008422542550171679</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.0880459477494783</v>
+        <v>-0.08833430377159868</v>
       </c>
       <c r="E57" t="n">
         <v>4</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3503,7 +3503,7 @@
         <v>0.01344620520425331</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>62671</v>
@@ -6570,7 +6570,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -9896,7 +9896,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13407,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -16474,7 +16474,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -19541,7 +19541,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -23089,7 +23089,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>36795</v>
@@ -26650,7 +26650,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>110406</v>
@@ -30198,7 +30198,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>38360</v>
@@ -33709,7 +33709,7 @@
         <v>0.01897309465108801</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -37220,7 +37220,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -40731,7 +40731,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>56757</v>
@@ -44279,7 +44279,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -47346,7 +47346,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -50672,7 +50672,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>43042</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -26668,7 +26668,7 @@
         <v>21006</v>
       </c>
       <c r="K56" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -23107,7 +23107,7 @@
         <v>5628</v>
       </c>
       <c r="K56" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -26668,7 +26668,7 @@
         <v>21006</v>
       </c>
       <c r="K56" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57">
@@ -50690,7 +50690,7 @@
         <v>7486</v>
       </c>
       <c r="K56" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -23107,7 +23107,7 @@
         <v>5628</v>
       </c>
       <c r="K56" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57">
@@ -26668,7 +26668,7 @@
         <v>21006</v>
       </c>
       <c r="K56" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3503,7 +3503,7 @@
         <v>0.01344620520425331</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>62671</v>
@@ -3521,7 +3521,7 @@
         <v>12269</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -6570,7 +6570,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -9896,7 +9896,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13407,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -16474,7 +16474,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -19541,7 +19541,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -23089,7 +23089,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>36795</v>
@@ -26650,7 +26650,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>110406</v>
@@ -26668,7 +26668,7 @@
         <v>21006</v>
       </c>
       <c r="K56" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57">
@@ -30198,7 +30198,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>38360</v>
@@ -33709,7 +33709,7 @@
         <v>0.01897309465108801</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -37220,7 +37220,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -40731,7 +40731,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>56757</v>
@@ -44279,7 +44279,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -47346,7 +47346,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -50672,7 +50672,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>43042</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -26668,7 +26668,7 @@
         <v>21006</v>
       </c>
       <c r="K56" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57">
@@ -50690,7 +50690,7 @@
         <v>7486</v>
       </c>
       <c r="K56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3521,7 +3521,7 @@
         <v>12269</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -26668,7 +26668,7 @@
         <v>21006</v>
       </c>
       <c r="K56" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57">
@@ -30216,7 +30216,7 @@
         <v>3382</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -50690,7 +50690,7 @@
         <v>7486</v>
       </c>
       <c r="K56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3521,7 +3521,7 @@
         <v>12269</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -23107,7 +23107,7 @@
         <v>5628</v>
       </c>
       <c r="K56" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
@@ -30216,7 +30216,7 @@
         <v>3382</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -37238,7 +37238,7 @@
         <v>523</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3503,7 +3503,7 @@
         <v>0.01344620520425331</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>62671</v>
@@ -6570,7 +6570,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -9896,7 +9896,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13407,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -16474,7 +16474,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -19541,7 +19541,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -23089,7 +23089,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>36795</v>
@@ -26650,7 +26650,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>110406</v>
@@ -30198,7 +30198,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>38360</v>
@@ -33709,7 +33709,7 @@
         <v>0.01897309465108801</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -37220,7 +37220,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -40731,7 +40731,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
         <v>56757</v>
@@ -44279,7 +44279,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -47346,7 +47346,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -50672,7 +50672,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>43042</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3494,16 +3494,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>152399</v>
+        <v>152507</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.01344620520425331</v>
+        <v>0.01416440014097901</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>62671</v>
@@ -3518,10 +3518,10 @@
         <v>0.01198716095958136</v>
       </c>
       <c r="J56" t="n">
-        <v>12269</v>
+        <v>12294</v>
       </c>
       <c r="K56" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.116759296320842</v>
+        <v>-0.1173847757807838</v>
       </c>
       <c r="E57" t="n">
         <v>4</v>
@@ -6570,7 +6570,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -9896,7 +9896,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -9914,7 +9914,7 @@
         <v>745</v>
       </c>
       <c r="K56" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
@@ -13407,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -13422,10 +13422,10 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="K55" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -16474,7 +16474,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -19541,7 +19541,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -23089,7 +23089,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>36795</v>
@@ -23104,10 +23104,10 @@
         <v>0.1792611820312651</v>
       </c>
       <c r="J56" t="n">
-        <v>5628</v>
+        <v>5677</v>
       </c>
       <c r="K56" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -26650,25 +26650,25 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>110406</v>
+        <v>108784</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>885</v>
+        <v>1008</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.006766597613598328</v>
+        <v>-0.006793736374080674</v>
       </c>
       <c r="J56" t="n">
-        <v>21006</v>
+        <v>21099</v>
       </c>
       <c r="K56" t="n">
-        <v>96</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -26699,7 +26699,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.6935331697980969</v>
+        <v>-0.6893489507432236</v>
       </c>
       <c r="J57" t="n">
         <v>4586</v>
@@ -30198,7 +30198,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>38360</v>
@@ -30207,16 +30207,16 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.4716540258944304</v>
+        <v>0.4724201333026891</v>
       </c>
       <c r="J56" t="n">
-        <v>3382</v>
+        <v>3385</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -30247,7 +30247,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.7870324578984357</v>
+        <v>-0.787143265953849</v>
       </c>
       <c r="J57" t="n">
         <v>2644</v>
@@ -33709,7 +33709,7 @@
         <v>0.01897309465108801</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -37220,7 +37220,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -40731,7 +40731,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F55" t="n">
         <v>56757</v>
@@ -40749,7 +40749,7 @@
         <v>3133</v>
       </c>
       <c r="K55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
@@ -44279,7 +44279,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -44297,7 +44297,7 @@
         <v>313</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -47346,7 +47346,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -50672,7 +50672,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>43042</v>
@@ -50690,7 +50690,7 @@
         <v>7486</v>
       </c>
       <c r="K56" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -9911,10 +9911,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="K56" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -26665,10 +26665,10 @@
         <v>-0.006793736374080674</v>
       </c>
       <c r="J56" t="n">
-        <v>21099</v>
+        <v>21104</v>
       </c>
       <c r="K56" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
@@ -33724,10 +33724,10 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -37235,10 +37235,10 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="K55" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -40746,10 +40746,10 @@
         <v>0.00147918574346693</v>
       </c>
       <c r="J55" t="n">
-        <v>3133</v>
+        <v>3141</v>
       </c>
       <c r="K55" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -44294,10 +44294,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -50687,10 +50687,10 @@
         <v>0.005439437076128972</v>
       </c>
       <c r="J56" t="n">
-        <v>7486</v>
+        <v>7507</v>
       </c>
       <c r="K56" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3503,7 +3503,7 @@
         <v>0.01416440014097901</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>62671</v>
@@ -6570,7 +6570,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -9896,7 +9896,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13407,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -16474,7 +16474,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -19541,7 +19541,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -23089,7 +23089,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>36795</v>
@@ -23104,10 +23104,10 @@
         <v>0.1792611820312651</v>
       </c>
       <c r="J56" t="n">
-        <v>5677</v>
+        <v>5671</v>
       </c>
       <c r="K56" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
@@ -26650,7 +26650,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>108784</v>
@@ -26665,10 +26665,10 @@
         <v>-0.006793736374080674</v>
       </c>
       <c r="J56" t="n">
-        <v>21104</v>
+        <v>21120</v>
       </c>
       <c r="K56" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -30198,7 +30198,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>38360</v>
@@ -33709,7 +33709,7 @@
         <v>0.01897309465108801</v>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -37220,7 +37220,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -40731,7 +40731,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F55" t="n">
         <v>56757</v>
@@ -44279,7 +44279,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -47346,7 +47346,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -50672,7 +50672,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>43042</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3518,10 +3518,10 @@
         <v>0.01198716095958136</v>
       </c>
       <c r="J56" t="n">
-        <v>12294</v>
+        <v>12296</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -26665,7 +26665,7 @@
         <v>-0.006793736374080674</v>
       </c>
       <c r="J56" t="n">
-        <v>21120</v>
+        <v>21119</v>
       </c>
       <c r="K56" t="n">
         <v>4</v>
@@ -50687,10 +50687,10 @@
         <v>0.005439437076128972</v>
       </c>
       <c r="J56" t="n">
-        <v>7507</v>
+        <v>7510</v>
       </c>
       <c r="K56" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.01416440014097901</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>62671</v>
@@ -6829,7 +6829,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20022,7 +20022,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -23607,7 +23607,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>36795</v>
@@ -27205,7 +27205,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>108784</v>
@@ -27223,7 +27223,7 @@
         <v>21119</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -30790,7 +30790,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>38360</v>
@@ -34338,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -37886,7 +37886,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -41434,7 +41434,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
         <v>56757</v>
@@ -45019,7 +45019,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -48049,7 +48049,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -51486,7 +51486,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>43042</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -27223,7 +27223,7 @@
         <v>21119</v>
       </c>
       <c r="K64" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -51489,22 +51489,22 @@
         <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>43042</v>
+        <v>20842</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.005439437076128972</v>
+        <v>-0.5175797976992339</v>
       </c>
       <c r="J64" t="n">
         <v>7510</v>
       </c>
       <c r="K64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -51535,7 +51535,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.8593627699249505</v>
+        <v>-0.7068899337875444</v>
       </c>
       <c r="J65" t="n">
         <v>5118</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -23625,7 +23625,7 @@
         <v>5671</v>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
@@ -27223,7 +27223,7 @@
         <v>21119</v>
       </c>
       <c r="K64" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
@@ -51504,7 +51504,7 @@
         <v>7510</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -23625,7 +23625,7 @@
         <v>5671</v>
       </c>
       <c r="K64" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3790,34 +3790,34 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>152507</v>
+        <v>152732</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.01416440014097901</v>
+        <v>0.01566063959249087</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
-        <v>62671</v>
+        <v>63824</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>3854</v>
+        <v>3884</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.01198716095958136</v>
+        <v>0.02998311453215084</v>
       </c>
       <c r="J64" t="n">
         <v>12296</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.1173847757807838</v>
+        <v>-0.1186850168923343</v>
       </c>
       <c r="E65" t="n">
         <v>16</v>
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.4117700112739572</v>
+        <v>-0.4220476162344184</v>
       </c>
       <c r="J65" t="n">
         <v>9470</v>
@@ -6829,7 +6829,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10281,10 +10281,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -13814,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
         <v>546</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20022,7 +20022,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -23607,7 +23607,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>36795</v>
@@ -23625,7 +23625,7 @@
         <v>5671</v>
       </c>
       <c r="K64" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65">
@@ -27205,25 +27205,25 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
-        <v>108784</v>
+        <v>110702</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1008</v>
+        <v>721</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>-0.006793736374080674</v>
+        <v>0.007960703074821563</v>
       </c>
       <c r="J64" t="n">
         <v>21119</v>
       </c>
       <c r="K64" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65">
@@ -27254,7 +27254,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.6893489507432236</v>
+        <v>-0.6938962332732022</v>
       </c>
       <c r="J65" t="n">
         <v>4586</v>
@@ -30790,7 +30790,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>38360</v>
@@ -34338,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -37886,7 +37886,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -41434,7 +41434,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F63" t="n">
         <v>56757</v>
@@ -45019,7 +45019,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -48049,7 +48049,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -51486,10 +51486,10 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
-        <v>20842</v>
+        <v>52385</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -51498,13 +51498,13 @@
         <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>-0.5175797976992339</v>
+        <v>0.2125315371617712</v>
       </c>
       <c r="J64" t="n">
         <v>7510</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -51535,7 +51535,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.7068899337875444</v>
+        <v>-0.8833826477044956</v>
       </c>
       <c r="J65" t="n">
         <v>5118</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3817,7 +3817,7 @@
         <v>12296</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -10284,7 +10284,7 @@
         <v>762</v>
       </c>
       <c r="K64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -23625,7 +23625,7 @@
         <v>5671</v>
       </c>
       <c r="K64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65">
@@ -27223,7 +27223,7 @@
         <v>21119</v>
       </c>
       <c r="K64" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
@@ -30808,7 +30808,7 @@
         <v>3385</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -37904,7 +37904,7 @@
         <v>529</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -51504,7 +51504,7 @@
         <v>7510</v>
       </c>
       <c r="K64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3817,7 +3817,7 @@
         <v>12296</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
@@ -10284,7 +10284,7 @@
         <v>762</v>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -2541,7 +2541,7 @@
         <v>0.01425992270585912</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>40886</v>
@@ -3799,7 +3799,7 @@
         <v>0.01566063959249087</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>63824</v>
@@ -5867,7 +5867,7 @@
         <v>-0.4882323485227842</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -9008,7 +9008,7 @@
         <v>0.1825533379215416</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -12556,7 +12556,7 @@
         <v>-0.5361966236345581</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -15882,7 +15882,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -18764,7 +18764,7 @@
         <v>0.0186880956830499</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>18875</v>
@@ -20022,7 +20022,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -22349,7 +22349,7 @@
         <v>0.03767525535616052</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>33267</v>
@@ -23607,7 +23607,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>36795</v>
@@ -23625,7 +23625,7 @@
         <v>5671</v>
       </c>
       <c r="K64" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65">
@@ -25947,7 +25947,7 @@
         <v>0.00289162432980582</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>71324</v>
@@ -27205,7 +27205,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>110702</v>
@@ -27220,10 +27220,10 @@
         <v>0.007960703074821563</v>
       </c>
       <c r="J64" t="n">
-        <v>21119</v>
+        <v>21128</v>
       </c>
       <c r="K64" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
@@ -29532,7 +29532,7 @@
         <v>0.05226338383264815</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>18875</v>
@@ -30790,7 +30790,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>38360</v>
@@ -33080,7 +33080,7 @@
         <v>0.09378305323774827</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -34338,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -36628,7 +36628,7 @@
         <v>0.03606497201064513</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -37886,7 +37886,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -40176,7 +40176,7 @@
         <v>0.0118006509177054</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>56747</v>
@@ -41434,7 +41434,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F63" t="n">
         <v>56757</v>
@@ -41452,7 +41452,7 @@
         <v>3141</v>
       </c>
       <c r="K63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -43761,7 +43761,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -45019,7 +45019,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -47087,7 +47087,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -48049,7 +48049,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -50228,7 +50228,7 @@
         <v>0.02457378877572281</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>43203</v>
@@ -51486,7 +51486,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>52385</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.01566063959249087</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>63824</v>
@@ -3817,7 +3817,7 @@
         <v>12296</v>
       </c>
       <c r="K64" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
@@ -6829,7 +6829,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20022,7 +20022,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -23607,7 +23607,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>36795</v>
@@ -23625,7 +23625,7 @@
         <v>5671</v>
       </c>
       <c r="K64" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65">
@@ -27205,7 +27205,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>110702</v>
@@ -30790,7 +30790,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>38360</v>
@@ -34338,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -37886,7 +37886,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -41434,7 +41434,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F63" t="n">
         <v>56757</v>
@@ -45019,7 +45019,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -48049,7 +48049,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -51486,7 +51486,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>52385</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.01566063959249087</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>63824</v>
@@ -3817,7 +3817,7 @@
         <v>12296</v>
       </c>
       <c r="K64" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
@@ -6829,7 +6829,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20022,7 +20022,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -23607,7 +23607,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>36795</v>
@@ -27205,7 +27205,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>110702</v>
@@ -30790,7 +30790,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>38360</v>
@@ -30808,7 +30808,7 @@
         <v>3385</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -34338,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -37886,7 +37886,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -41434,7 +41434,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
         <v>56757</v>
@@ -41452,7 +41452,7 @@
         <v>3141</v>
       </c>
       <c r="K63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -45019,7 +45019,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -48049,7 +48049,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -51486,7 +51486,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>52385</v>
@@ -51504,7 +51504,7 @@
         <v>7510</v>
       </c>
       <c r="K64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3817,7 +3817,7 @@
         <v>12296</v>
       </c>
       <c r="K64" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
@@ -27208,7 +27208,7 @@
         <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>110702</v>
+        <v>110578</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -27217,13 +27217,13 @@
         <v>721</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.007960703074821563</v>
+        <v>0.006838967641551252</v>
       </c>
       <c r="J64" t="n">
-        <v>21128</v>
+        <v>21125</v>
       </c>
       <c r="K64" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
@@ -27254,7 +27254,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.6938962332732022</v>
+        <v>-0.6935551981599116</v>
       </c>
       <c r="J65" t="n">
         <v>4586</v>
@@ -30808,7 +30808,7 @@
         <v>3385</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -41452,7 +41452,7 @@
         <v>3141</v>
       </c>
       <c r="K63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.01566063959249087</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>63824</v>
@@ -6829,7 +6829,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20022,7 +20022,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -23607,7 +23607,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>36795</v>
@@ -23625,7 +23625,7 @@
         <v>5671</v>
       </c>
       <c r="K64" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -27205,7 +27205,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>110578</v>
@@ -30790,7 +30790,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>38360</v>
@@ -30808,7 +30808,7 @@
         <v>3385</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -34338,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -37886,7 +37886,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -41434,7 +41434,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F63" t="n">
         <v>56757</v>
@@ -45019,7 +45019,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -48049,7 +48049,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -51486,7 +51486,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
         <v>52385</v>
